--- a/data/externalStats/File1/RPT_RPT8270621607594XL_externalStats.xlsx
+++ b/data/externalStats/File1/RPT_RPT8270621607594XL_externalStats.xlsx
@@ -4724,13 +4724,13 @@
         <v>1.293503069924508</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>365.1162246410076</v>
+        <v>365.1162246410071</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>592.6294401595056</v>
+        <v>592.6294401595051</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>94.84860814782851</v>
+        <v>94.84860814782856</v>
       </c>
       <c r="Q63" s="131" t="n">
         <v>26.22748476337624</v>
@@ -4739,13 +4739,13 @@
         <v>0.4164758392767124</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>413.5483367949295</v>
+        <v>413.5483367949288</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>535.040905545411</v>
+        <v>535.0409055454103</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>96.179119123939</v>
+        <v>96.17911912393895</v>
       </c>
       <c r="W63" s="131" t="n">
         <v>21.08529797588731</v>
@@ -4754,10 +4754,10 @@
         <v>0.4472220454100387</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>443.3225561741567</v>
+        <v>443.322556174156</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>561.034195319393</v>
+        <v>561.0341953193923</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -5135,13 +5135,13 @@
         <v>1.293503069924508</v>
       </c>
       <c r="M68" s="143" t="n">
-        <v>365.1162246410076</v>
+        <v>365.1162246410071</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>592.6294401595056</v>
+        <v>592.6294401595051</v>
       </c>
       <c r="P68" s="142" t="n">
-        <v>94.84860814782851</v>
+        <v>94.84860814782856</v>
       </c>
       <c r="Q68" s="143" t="n">
         <v>26.22748476337624</v>
@@ -5150,13 +5150,13 @@
         <v>0.4164758392767124</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>413.5483367949295</v>
+        <v>413.5483367949288</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>535.040905545411</v>
+        <v>535.0409055454103</v>
       </c>
       <c r="V68" s="142" t="n">
-        <v>96.179119123939</v>
+        <v>96.17911912393895</v>
       </c>
       <c r="W68" s="143" t="n">
         <v>21.08529797588731</v>
@@ -5165,10 +5165,10 @@
         <v>0.4472220454100387</v>
       </c>
       <c r="Y68" s="143" t="n">
-        <v>443.3225561741567</v>
+        <v>443.322556174156</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>561.034195319393</v>
+        <v>561.0341953193923</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -7220,13 +7220,13 @@
         <v>1.293503069924508</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>365.1162246410076</v>
+        <v>365.1162246410071</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>592.6294401595056</v>
+        <v>592.6294401595051</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>94.84860814782851</v>
+        <v>94.84860814782856</v>
       </c>
       <c r="Q99" s="131" t="n">
         <v>26.22748476337624</v>
@@ -7235,13 +7235,13 @@
         <v>0.4164758392767124</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>413.5483367949295</v>
+        <v>413.5483367949288</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>535.040905545411</v>
+        <v>535.0409055454103</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>96.179119123939</v>
+        <v>96.17911912393895</v>
       </c>
       <c r="W99" s="131" t="n">
         <v>21.08529797588731</v>
@@ -7250,10 +7250,10 @@
         <v>0.4472220454100387</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>443.3225561741567</v>
+        <v>443.322556174156</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>561.034195319393</v>
+        <v>561.0341953193923</v>
       </c>
     </row>
     <row r="100">
@@ -7559,13 +7559,13 @@
         <v>1.293503069924508</v>
       </c>
       <c r="M104" s="143" t="n">
-        <v>365.1162246410076</v>
+        <v>365.1162246410071</v>
       </c>
       <c r="N104" s="144" t="n">
-        <v>592.6294401595056</v>
+        <v>592.6294401595051</v>
       </c>
       <c r="P104" s="142" t="n">
-        <v>94.84860814782851</v>
+        <v>94.84860814782856</v>
       </c>
       <c r="Q104" s="143" t="n">
         <v>26.22748476337624</v>
@@ -7574,13 +7574,13 @@
         <v>0.4164758392767124</v>
       </c>
       <c r="S104" s="143" t="n">
-        <v>413.5483367949295</v>
+        <v>413.5483367949288</v>
       </c>
       <c r="T104" s="144" t="n">
-        <v>535.040905545411</v>
+        <v>535.0409055454103</v>
       </c>
       <c r="V104" s="142" t="n">
-        <v>96.179119123939</v>
+        <v>96.17911912393895</v>
       </c>
       <c r="W104" s="143" t="n">
         <v>21.08529797588731</v>
@@ -7589,10 +7589,10 @@
         <v>0.4472220454100387</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>443.3225561741567</v>
+        <v>443.322556174156</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>561.034195319393</v>
+        <v>561.0341953193923</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="H106" s="111" t="n">
-        <v>-520027</v>
+        <v>3772</v>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1" thickBot="1"/>
@@ -7614,7 +7614,7 @@
         </is>
       </c>
       <c r="H108" s="113" t="n">
-        <v>0</v>
+        <v>523799</v>
       </c>
     </row>
     <row r="109"/>
@@ -11248,13 +11248,13 @@
         <v>1.293503069924508</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>365.1162246410076</v>
+        <v>365.1162246410071</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>592.6294401595056</v>
+        <v>592.6294401595051</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>94.84860814782851</v>
+        <v>94.84860814782856</v>
       </c>
       <c r="Q63" s="131" t="n">
         <v>26.22748476337624</v>
@@ -11263,13 +11263,13 @@
         <v>0.4164758392767124</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>413.5483367949295</v>
+        <v>413.5483367949288</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>535.040905545411</v>
+        <v>535.0409055454103</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>96.179119123939</v>
+        <v>96.17911912393895</v>
       </c>
       <c r="W63" s="131" t="n">
         <v>21.08529797588731</v>
@@ -11278,10 +11278,10 @@
         <v>0.4472220454100387</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>443.3225561741567</v>
+        <v>443.322556174156</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>561.034195319393</v>
+        <v>561.0341953193923</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -11659,13 +11659,13 @@
         <v>1.293503069924508</v>
       </c>
       <c r="M68" s="143" t="n">
-        <v>365.1162246410076</v>
+        <v>365.1162246410071</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>592.6294401595056</v>
+        <v>592.6294401595051</v>
       </c>
       <c r="P68" s="142" t="n">
-        <v>94.84860814782851</v>
+        <v>94.84860814782856</v>
       </c>
       <c r="Q68" s="143" t="n">
         <v>26.22748476337624</v>
@@ -11674,13 +11674,13 @@
         <v>0.4164758392767124</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>413.5483367949295</v>
+        <v>413.5483367949288</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>535.040905545411</v>
+        <v>535.0409055454103</v>
       </c>
       <c r="V68" s="142" t="n">
-        <v>96.179119123939</v>
+        <v>96.17911912393895</v>
       </c>
       <c r="W68" s="143" t="n">
         <v>21.08529797588731</v>
@@ -11689,10 +11689,10 @@
         <v>0.4472220454100387</v>
       </c>
       <c r="Y68" s="143" t="n">
-        <v>443.3225561741567</v>
+        <v>443.322556174156</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>561.034195319393</v>
+        <v>561.0341953193923</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -13744,13 +13744,13 @@
         <v>1.293503069924508</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>365.1162246410076</v>
+        <v>365.1162246410071</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>592.6294401595056</v>
+        <v>592.6294401595051</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>94.84860814782851</v>
+        <v>94.84860814782856</v>
       </c>
       <c r="Q99" s="131" t="n">
         <v>26.22748476337624</v>
@@ -13759,13 +13759,13 @@
         <v>0.4164758392767124</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>413.5483367949295</v>
+        <v>413.5483367949288</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>535.040905545411</v>
+        <v>535.0409055454103</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>96.179119123939</v>
+        <v>96.17911912393895</v>
       </c>
       <c r="W99" s="131" t="n">
         <v>21.08529797588731</v>
@@ -13774,10 +13774,10 @@
         <v>0.4472220454100387</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>443.3225561741567</v>
+        <v>443.322556174156</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>561.034195319393</v>
+        <v>561.0341953193923</v>
       </c>
     </row>
     <row r="100">
@@ -14083,13 +14083,13 @@
         <v>1.293503069924508</v>
       </c>
       <c r="M104" s="143" t="n">
-        <v>365.1162246410076</v>
+        <v>365.1162246410071</v>
       </c>
       <c r="N104" s="144" t="n">
-        <v>592.6294401595056</v>
+        <v>592.6294401595051</v>
       </c>
       <c r="P104" s="142" t="n">
-        <v>94.84860814782851</v>
+        <v>94.84860814782856</v>
       </c>
       <c r="Q104" s="143" t="n">
         <v>26.22748476337624</v>
@@ -14098,13 +14098,13 @@
         <v>0.4164758392767124</v>
       </c>
       <c r="S104" s="143" t="n">
-        <v>413.5483367949295</v>
+        <v>413.5483367949288</v>
       </c>
       <c r="T104" s="144" t="n">
-        <v>535.040905545411</v>
+        <v>535.0409055454103</v>
       </c>
       <c r="V104" s="142" t="n">
-        <v>96.179119123939</v>
+        <v>96.17911912393895</v>
       </c>
       <c r="W104" s="143" t="n">
         <v>21.08529797588731</v>
@@ -14113,10 +14113,10 @@
         <v>0.4472220454100387</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>443.3225561741567</v>
+        <v>443.322556174156</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>561.034195319393</v>
+        <v>561.0341953193923</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -14127,7 +14127,7 @@
         </is>
       </c>
       <c r="H106" s="111" t="n">
-        <v>-520027</v>
+        <v>3772</v>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1" thickBot="1"/>
@@ -14138,7 +14138,7 @@
         </is>
       </c>
       <c r="H108" s="113" t="n">
-        <v>0</v>
+        <v>523799</v>
       </c>
     </row>
     <row r="109"/>
@@ -17772,13 +17772,13 @@
         <v>1.293503069924508</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>365.1162246410076</v>
+        <v>365.1162246410071</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>592.6294401595056</v>
+        <v>592.6294401595051</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>94.84860814782851</v>
+        <v>94.84860814782856</v>
       </c>
       <c r="Q63" s="131" t="n">
         <v>26.22748476337624</v>
@@ -17787,13 +17787,13 @@
         <v>0.4164758392767124</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>413.5483367949295</v>
+        <v>413.5483367949288</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>535.040905545411</v>
+        <v>535.0409055454103</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>96.179119123939</v>
+        <v>96.17911912393895</v>
       </c>
       <c r="W63" s="131" t="n">
         <v>21.08529797588731</v>
@@ -17802,10 +17802,10 @@
         <v>0.4472220454100387</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>443.3225561741567</v>
+        <v>443.322556174156</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>561.034195319393</v>
+        <v>561.0341953193923</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -18183,13 +18183,13 @@
         <v>1.293503069924508</v>
       </c>
       <c r="M68" s="143" t="n">
-        <v>365.1162246410076</v>
+        <v>365.1162246410071</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>592.6294401595056</v>
+        <v>592.6294401595051</v>
       </c>
       <c r="P68" s="142" t="n">
-        <v>94.84860814782851</v>
+        <v>94.84860814782856</v>
       </c>
       <c r="Q68" s="143" t="n">
         <v>26.22748476337624</v>
@@ -18198,13 +18198,13 @@
         <v>0.4164758392767124</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>413.5483367949295</v>
+        <v>413.5483367949288</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>535.040905545411</v>
+        <v>535.0409055454103</v>
       </c>
       <c r="V68" s="142" t="n">
-        <v>96.179119123939</v>
+        <v>96.17911912393895</v>
       </c>
       <c r="W68" s="143" t="n">
         <v>21.08529797588731</v>
@@ -18213,10 +18213,10 @@
         <v>0.4472220454100387</v>
       </c>
       <c r="Y68" s="143" t="n">
-        <v>443.3225561741567</v>
+        <v>443.322556174156</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>561.034195319393</v>
+        <v>561.0341953193923</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -20268,13 +20268,13 @@
         <v>1.293503069924508</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>365.1162246410076</v>
+        <v>365.1162246410071</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>592.6294401595056</v>
+        <v>592.6294401595051</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>94.84860814782851</v>
+        <v>94.84860814782856</v>
       </c>
       <c r="Q99" s="131" t="n">
         <v>26.22748476337624</v>
@@ -20283,13 +20283,13 @@
         <v>0.4164758392767124</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>413.5483367949295</v>
+        <v>413.5483367949288</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>535.040905545411</v>
+        <v>535.0409055454103</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>96.179119123939</v>
+        <v>96.17911912393895</v>
       </c>
       <c r="W99" s="131" t="n">
         <v>21.08529797588731</v>
@@ -20298,10 +20298,10 @@
         <v>0.4472220454100387</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>443.3225561741567</v>
+        <v>443.322556174156</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>561.034195319393</v>
+        <v>561.0341953193923</v>
       </c>
     </row>
     <row r="100">
@@ -20607,13 +20607,13 @@
         <v>1.293503069924508</v>
       </c>
       <c r="M104" s="143" t="n">
-        <v>365.1162246410076</v>
+        <v>365.1162246410071</v>
       </c>
       <c r="N104" s="144" t="n">
-        <v>592.6294401595056</v>
+        <v>592.6294401595051</v>
       </c>
       <c r="P104" s="142" t="n">
-        <v>94.84860814782851</v>
+        <v>94.84860814782856</v>
       </c>
       <c r="Q104" s="143" t="n">
         <v>26.22748476337624</v>
@@ -20622,13 +20622,13 @@
         <v>0.4164758392767124</v>
       </c>
       <c r="S104" s="143" t="n">
-        <v>413.5483367949295</v>
+        <v>413.5483367949288</v>
       </c>
       <c r="T104" s="144" t="n">
-        <v>535.040905545411</v>
+        <v>535.0409055454103</v>
       </c>
       <c r="V104" s="142" t="n">
-        <v>96.179119123939</v>
+        <v>96.17911912393895</v>
       </c>
       <c r="W104" s="143" t="n">
         <v>21.08529797588731</v>
@@ -20637,10 +20637,10 @@
         <v>0.4472220454100387</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>443.3225561741567</v>
+        <v>443.322556174156</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>561.034195319393</v>
+        <v>561.0341953193923</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -20651,7 +20651,7 @@
         </is>
       </c>
       <c r="H106" s="111" t="n">
-        <v>-520027</v>
+        <v>3772</v>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1" thickBot="1"/>
@@ -20662,7 +20662,7 @@
         </is>
       </c>
       <c r="H108" s="113" t="n">
-        <v>0</v>
+        <v>523799</v>
       </c>
     </row>
     <row r="109"/>
@@ -24296,13 +24296,13 @@
         <v>1.293503069924508</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>365.1162246410076</v>
+        <v>365.1162246410071</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>592.6294401595056</v>
+        <v>592.6294401595051</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>94.84860814782851</v>
+        <v>94.84860814782856</v>
       </c>
       <c r="Q63" s="131" t="n">
         <v>26.22748476337624</v>
@@ -24311,13 +24311,13 @@
         <v>0.4164758392767124</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>413.5483367949295</v>
+        <v>413.5483367949288</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>535.040905545411</v>
+        <v>535.0409055454103</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>96.179119123939</v>
+        <v>96.17911912393895</v>
       </c>
       <c r="W63" s="131" t="n">
         <v>21.08529797588731</v>
@@ -24326,10 +24326,10 @@
         <v>0.4472220454100387</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>443.3225561741567</v>
+        <v>443.322556174156</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>561.034195319393</v>
+        <v>561.0341953193923</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -24707,13 +24707,13 @@
         <v>1.293503069924508</v>
       </c>
       <c r="M68" s="143" t="n">
-        <v>365.1162246410076</v>
+        <v>365.1162246410071</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>592.6294401595056</v>
+        <v>592.6294401595051</v>
       </c>
       <c r="P68" s="142" t="n">
-        <v>94.84860814782851</v>
+        <v>94.84860814782856</v>
       </c>
       <c r="Q68" s="143" t="n">
         <v>26.22748476337624</v>
@@ -24722,13 +24722,13 @@
         <v>0.4164758392767124</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>413.5483367949295</v>
+        <v>413.5483367949288</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>535.040905545411</v>
+        <v>535.0409055454103</v>
       </c>
       <c r="V68" s="142" t="n">
-        <v>96.179119123939</v>
+        <v>96.17911912393895</v>
       </c>
       <c r="W68" s="143" t="n">
         <v>21.08529797588731</v>
@@ -24737,10 +24737,10 @@
         <v>0.4472220454100387</v>
       </c>
       <c r="Y68" s="143" t="n">
-        <v>443.3225561741567</v>
+        <v>443.322556174156</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>561.034195319393</v>
+        <v>561.0341953193923</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -26792,13 +26792,13 @@
         <v>1.293503069924508</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>365.1162246410076</v>
+        <v>365.1162246410071</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>592.6294401595056</v>
+        <v>592.6294401595051</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>94.84860814782851</v>
+        <v>94.84860814782856</v>
       </c>
       <c r="Q99" s="131" t="n">
         <v>26.22748476337624</v>
@@ -26807,13 +26807,13 @@
         <v>0.4164758392767124</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>413.5483367949295</v>
+        <v>413.5483367949288</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>535.040905545411</v>
+        <v>535.0409055454103</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>96.179119123939</v>
+        <v>96.17911912393895</v>
       </c>
       <c r="W99" s="131" t="n">
         <v>21.08529797588731</v>
@@ -26822,10 +26822,10 @@
         <v>0.4472220454100387</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>443.3225561741567</v>
+        <v>443.322556174156</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>561.034195319393</v>
+        <v>561.0341953193923</v>
       </c>
     </row>
     <row r="100">
@@ -27131,13 +27131,13 @@
         <v>1.293503069924508</v>
       </c>
       <c r="M104" s="143" t="n">
-        <v>365.1162246410076</v>
+        <v>365.1162246410071</v>
       </c>
       <c r="N104" s="144" t="n">
-        <v>592.6294401595056</v>
+        <v>592.6294401595051</v>
       </c>
       <c r="P104" s="142" t="n">
-        <v>94.84860814782851</v>
+        <v>94.84860814782856</v>
       </c>
       <c r="Q104" s="143" t="n">
         <v>26.22748476337624</v>
@@ -27146,13 +27146,13 @@
         <v>0.4164758392767124</v>
       </c>
       <c r="S104" s="143" t="n">
-        <v>413.5483367949295</v>
+        <v>413.5483367949288</v>
       </c>
       <c r="T104" s="144" t="n">
-        <v>535.040905545411</v>
+        <v>535.0409055454103</v>
       </c>
       <c r="V104" s="142" t="n">
-        <v>96.179119123939</v>
+        <v>96.17911912393895</v>
       </c>
       <c r="W104" s="143" t="n">
         <v>21.08529797588731</v>
@@ -27161,10 +27161,10 @@
         <v>0.4472220454100387</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>443.3225561741567</v>
+        <v>443.322556174156</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>561.034195319393</v>
+        <v>561.0341953193923</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -27175,7 +27175,7 @@
         </is>
       </c>
       <c r="H106" s="111" t="n">
-        <v>-520027</v>
+        <v>3772</v>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1" thickBot="1"/>
@@ -27186,7 +27186,7 @@
         </is>
       </c>
       <c r="H108" s="113" t="n">
-        <v>0</v>
+        <v>523799</v>
       </c>
     </row>
     <row r="109"/>
@@ -30820,13 +30820,13 @@
         <v>1.293503069924508</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>365.1162246410076</v>
+        <v>365.1162246410071</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>592.6294401595056</v>
+        <v>592.6294401595051</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>94.84860814782851</v>
+        <v>94.84860814782856</v>
       </c>
       <c r="Q63" s="131" t="n">
         <v>26.22748476337624</v>
@@ -30835,13 +30835,13 @@
         <v>0.4164758392767124</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>413.5483367949295</v>
+        <v>413.5483367949288</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>535.040905545411</v>
+        <v>535.0409055454103</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>96.179119123939</v>
+        <v>96.17911912393895</v>
       </c>
       <c r="W63" s="131" t="n">
         <v>21.08529797588731</v>
@@ -30850,10 +30850,10 @@
         <v>0.4472220454100387</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>443.3225561741567</v>
+        <v>443.322556174156</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>561.034195319393</v>
+        <v>561.0341953193923</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -31231,13 +31231,13 @@
         <v>1.293503069924508</v>
       </c>
       <c r="M68" s="143" t="n">
-        <v>365.1162246410076</v>
+        <v>365.1162246410071</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>592.6294401595056</v>
+        <v>592.6294401595051</v>
       </c>
       <c r="P68" s="142" t="n">
-        <v>94.84860814782851</v>
+        <v>94.84860814782856</v>
       </c>
       <c r="Q68" s="143" t="n">
         <v>26.22748476337624</v>
@@ -31246,13 +31246,13 @@
         <v>0.4164758392767124</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>413.5483367949295</v>
+        <v>413.5483367949288</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>535.040905545411</v>
+        <v>535.0409055454103</v>
       </c>
       <c r="V68" s="142" t="n">
-        <v>96.179119123939</v>
+        <v>96.17911912393895</v>
       </c>
       <c r="W68" s="143" t="n">
         <v>21.08529797588731</v>
@@ -31261,10 +31261,10 @@
         <v>0.4472220454100387</v>
       </c>
       <c r="Y68" s="143" t="n">
-        <v>443.3225561741567</v>
+        <v>443.322556174156</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>561.034195319393</v>
+        <v>561.0341953193923</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -33316,13 +33316,13 @@
         <v>1.293503069924508</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>365.1162246410076</v>
+        <v>365.1162246410071</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>592.6294401595056</v>
+        <v>592.6294401595051</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>94.84860814782851</v>
+        <v>94.84860814782856</v>
       </c>
       <c r="Q99" s="131" t="n">
         <v>26.22748476337624</v>
@@ -33331,13 +33331,13 @@
         <v>0.4164758392767124</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>413.5483367949295</v>
+        <v>413.5483367949288</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>535.040905545411</v>
+        <v>535.0409055454103</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>96.179119123939</v>
+        <v>96.17911912393895</v>
       </c>
       <c r="W99" s="131" t="n">
         <v>21.08529797588731</v>
@@ -33346,10 +33346,10 @@
         <v>0.4472220454100387</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>443.3225561741567</v>
+        <v>443.322556174156</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>561.034195319393</v>
+        <v>561.0341953193923</v>
       </c>
     </row>
     <row r="100">
@@ -33655,13 +33655,13 @@
         <v>1.293503069924508</v>
       </c>
       <c r="M104" s="143" t="n">
-        <v>365.1162246410076</v>
+        <v>365.1162246410071</v>
       </c>
       <c r="N104" s="144" t="n">
-        <v>592.6294401595056</v>
+        <v>592.6294401595051</v>
       </c>
       <c r="P104" s="142" t="n">
-        <v>94.84860814782851</v>
+        <v>94.84860814782856</v>
       </c>
       <c r="Q104" s="143" t="n">
         <v>26.22748476337624</v>
@@ -33670,13 +33670,13 @@
         <v>0.4164758392767124</v>
       </c>
       <c r="S104" s="143" t="n">
-        <v>413.5483367949295</v>
+        <v>413.5483367949288</v>
       </c>
       <c r="T104" s="144" t="n">
-        <v>535.040905545411</v>
+        <v>535.0409055454103</v>
       </c>
       <c r="V104" s="142" t="n">
-        <v>96.179119123939</v>
+        <v>96.17911912393895</v>
       </c>
       <c r="W104" s="143" t="n">
         <v>21.08529797588731</v>
@@ -33685,10 +33685,10 @@
         <v>0.4472220454100387</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>443.3225561741567</v>
+        <v>443.322556174156</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>561.034195319393</v>
+        <v>561.0341953193923</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -33699,7 +33699,7 @@
         </is>
       </c>
       <c r="H106" s="111" t="n">
-        <v>-520027</v>
+        <v>3772</v>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1" thickBot="1"/>
@@ -33710,7 +33710,7 @@
         </is>
       </c>
       <c r="H108" s="113" t="n">
-        <v>0</v>
+        <v>523799</v>
       </c>
     </row>
     <row r="109"/>
